--- a/Pipe_Matlab_Indici_di_Prestazione_Guasto_Buffer_Ridotto/FOLDER/EXCEL.xlsx
+++ b/Pipe_Matlab_Indici_di_Prestazione_Guasto_Buffer_Ridotto/FOLDER/EXCEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lachiara\Documents\GitHub\ControlloAvanzato\Pipe_Matlab_Indici_di_Prestazione_Guasto_Buffer_Ridotto\FOLDER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3285623A-F2F0-4FFF-9D7F-1D407531C9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1216F1E8-3178-4512-982D-7E1E452E96D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8669,7 +8669,7 @@
         <v>1</v>
       </c>
       <c r="J133" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133" s="5">
         <v>0</v>
@@ -8764,7 +8764,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134" s="6">
         <v>0</v>
